--- a/artfynd/A 5909-2025 artfynd.xlsx
+++ b/artfynd/A 5909-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,48 +1543,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134910652</v>
+        <v>134675769</v>
       </c>
       <c r="B10" t="n">
-        <v>43472</v>
+        <v>99173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101242</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Anga Sudebys, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717516</v>
+        <v>717589</v>
       </c>
       <c r="R10" t="n">
-        <v>6374628</v>
+        <v>6374669</v>
       </c>
       <c r="S10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,27 +1608,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:59</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1st</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,234 +1638,15 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>134910654</v>
-      </c>
-      <c r="B11" t="n">
-        <v>43472</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>101242</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Dårgräsfjäril</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lopinga achine</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Anga Sudebys, Gtl</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>717541</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6374625</v>
-      </c>
-      <c r="S11" t="n">
-        <v>22</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Anga</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Esmeralda  Svanberg</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Esmeralda  Svanberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>134675769</v>
-      </c>
-      <c r="B12" t="n">
-        <v>99173</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>219798</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ange Sudebys, Gtl</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>717589</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6374669</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Anga</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5909-2025 artfynd.xlsx
+++ b/artfynd/A 5909-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,48 +1543,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134675769</v>
+        <v>134910652</v>
       </c>
       <c r="B10" t="n">
-        <v>99173</v>
+        <v>43472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ange Sudebys, Gtl</t>
+          <t>Anga Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717589</v>
+        <v>717516</v>
       </c>
       <c r="R10" t="n">
-        <v>6374669</v>
+        <v>6374628</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,22 +1608,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,15 +1643,234 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134910654</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>717541</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6374625</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134675769</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>717589</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6374669</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5909-2025 artfynd.xlsx
+++ b/artfynd/A 5909-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134886308</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675758</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675763</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134886304</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134886310</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134886311</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134886312</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,51 +1580,56 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134886313</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134910652</v>
+        <v>134675769</v>
       </c>
       <c r="B10" t="n">
-        <v>43472</v>
+        <v>99173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101242</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Anga Sudebys, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717516</v>
+        <v>717589</v>
       </c>
       <c r="R10" t="n">
-        <v>6374628</v>
+        <v>6374669</v>
       </c>
       <c r="S10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,27 +1653,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:59</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:59</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1st</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,236 +1683,33 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>134910654</v>
-      </c>
-      <c r="B11" t="n">
-        <v>43472</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>101242</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Dårgräsfjäril</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lopinga achine</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Anga Sudebys, Gtl</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>717541</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6374625</v>
-      </c>
-      <c r="S11" t="n">
-        <v>22</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Anga</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Esmeralda  Svanberg</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Esmeralda  Svanberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>134675769</v>
-      </c>
-      <c r="B12" t="n">
-        <v>99173</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>219798</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Skogsknipprot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Epipactis helleborine</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ange Sudebys, Gtl</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>717589</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6374669</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Anga</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 5909-2025 artfynd.xlsx
+++ b/artfynd/A 5909-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,48 +1588,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134675769</v>
+        <v>134910652</v>
       </c>
       <c r="B10" t="n">
-        <v>99173</v>
+        <v>43477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ange Sudebys, Gtl</t>
+          <t>Anga Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717589</v>
+        <v>717516</v>
       </c>
       <c r="R10" t="n">
-        <v>6374669</v>
+        <v>6374628</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,22 +1653,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>23:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,16 +1688,245 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134910652</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134910654</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43477</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>717541</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6374625</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134910654</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134675769</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99173</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>717589</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6374669</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134675769</t>
         </is>
@@ -1709,6 +1943,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
